--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0006_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1022,7 +1023,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B26" s="0">
         <v>0.087719298245613961</v>
@@ -1060,7 +1061,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B27" s="0">
         <v>0.26315789473684187</v>
@@ -1163,7 +1164,7 @@
         <v>0.77257651287958895</v>
       </c>
       <c r="J29" s="0">
-        <v>1.0489510489510538</v>
+        <v>1.0489510489510539</v>
       </c>
       <c r="K29" s="0">
         <v>1.5463917525773268</v>
@@ -1186,7 +1187,7 @@
         <v>0.67078594955881943</v>
       </c>
       <c r="E30" s="0">
-        <v>0.25537754706285964</v>
+        <v>0.25537754706285965</v>
       </c>
       <c r="F30" s="0">
         <v>0.97878688643888867</v>
@@ -1391,7 +1392,7 @@
         <v>4.7844134178070172</v>
       </c>
       <c r="J35" s="0">
-        <v>5.3183658446816588</v>
+        <v>5.3183658446816589</v>
       </c>
       <c r="K35" s="0">
         <v>11.855670103092839</v>
@@ -1408,7 +1409,7 @@
         <v>8.0701754385964843</v>
       </c>
       <c r="C36" s="0">
-        <v>4.4738076820654546</v>
+        <v>4.4738076820654547</v>
       </c>
       <c r="D36" s="0">
         <v>5.8856057509677058</v>
@@ -1432,7 +1433,7 @@
         <v>4.4534412955465541</v>
       </c>
       <c r="K36" s="0">
-        <v>8.2474226804123631</v>
+        <v>8.2474226804123632</v>
       </c>
       <c r="L36" s="0">
         <v>4.3386309209093978</v>
@@ -1443,7 +1444,7 @@
         <v>3.5295855075317486</v>
       </c>
       <c r="B37" s="0">
-        <v>4.5614035087719262</v>
+        <v>4.5614035087719263</v>
       </c>
       <c r="C37" s="0">
         <v>4.567646051813993</v>
@@ -1473,7 +1474,7 @@
         <v>8.376288659793806</v>
       </c>
       <c r="L37" s="0">
-        <v>4.1691288526731531</v>
+        <v>4.1691288526731532</v>
       </c>
     </row>
     <row r="38">
@@ -1502,7 +1503,7 @@
         <v>3.8345736522183684</v>
       </c>
       <c r="I38" s="0">
-        <v>4.5639609938233558</v>
+        <v>4.5639609938233559</v>
       </c>
       <c r="J38" s="0">
         <v>3.7541405962458558</v>
@@ -1511,7 +1512,7 @@
         <v>5.5412371134020564</v>
       </c>
       <c r="L38" s="0">
-        <v>4.0929306752091525</v>
+        <v>4.0929306752091526</v>
       </c>
     </row>
     <row r="39">
@@ -1560,13 +1561,13 @@
         <v>1.4035087719298234</v>
       </c>
       <c r="C40" s="0">
-        <v>4.1022584613043493</v>
+        <v>4.1022584613043494</v>
       </c>
       <c r="D40" s="0">
         <v>3.7554396172432831</v>
       </c>
       <c r="E40" s="0">
-        <v>3.8748172678182486</v>
+        <v>3.8748172678182487</v>
       </c>
       <c r="F40" s="0">
         <v>3.6440708801804718</v>
@@ -1867,7 +1868,7 @@
         <v>2.5513891882980992</v>
       </c>
       <c r="D48" s="0">
-        <v>3.1760151948645174</v>
+        <v>3.1760151948645175</v>
       </c>
       <c r="E48" s="0">
         <v>2.8724007279453421</v>
@@ -1978,7 +1979,7 @@
         <v>3.1578947368421026</v>
       </c>
       <c r="C51" s="0">
-        <v>2.3003081449168747</v>
+        <v>2.3003081449168748</v>
       </c>
       <c r="D51" s="0">
         <v>1.8729113071911123</v>
@@ -2133,7 +2134,7 @@
         <v>1.8197035214750361</v>
       </c>
       <c r="D55" s="0">
-        <v>1.6565287428172994</v>
+        <v>1.6565287428172995</v>
       </c>
       <c r="E55" s="0">
         <v>2.2470837435484334</v>
@@ -2358,7 +2359,7 @@
         <v>0.61403508771929771</v>
       </c>
       <c r="C61" s="0">
-        <v>1.349243586654661</v>
+        <v>1.3492435866546611</v>
       </c>
       <c r="D61" s="0">
         <v>0.91842377323107172</v>
@@ -2449,7 +2450,7 @@
         <v>1.2472339569503106</v>
       </c>
       <c r="H63" s="0">
-        <v>1.2043401692893247</v>
+        <v>1.2043401692893248</v>
       </c>
       <c r="I63" s="0">
         <v>0.90365633254552957</v>
@@ -2715,7 +2716,7 @@
         <v>0.78455039227519552</v>
       </c>
       <c r="H70" s="0">
-        <v>0.90893597682213167</v>
+        <v>0.90893597682213168</v>
       </c>
       <c r="I70" s="0">
         <v>0.54815197314849706</v>
@@ -2738,7 +2739,7 @@
         <v>0.96491228070175361</v>
       </c>
       <c r="C71" s="0">
-        <v>0.74056226936684399</v>
+        <v>0.740562269366844</v>
       </c>
       <c r="D71" s="0">
         <v>0.3534248551438941</v>
@@ -2756,7 +2757,7 @@
         <v>0.73282963131284373</v>
       </c>
       <c r="I71" s="0">
-        <v>0.50445869992651537</v>
+        <v>0.50445869992651538</v>
       </c>
       <c r="J71" s="0">
         <v>0.60728744939271206</v>
@@ -2785,7 +2786,7 @@
         <v>0.7583758465348005</v>
       </c>
       <c r="F72" s="0">
-        <v>0.71316814030491515</v>
+        <v>0.71316814030491516</v>
       </c>
       <c r="G72" s="0">
         <v>0.64373365520016035</v>
@@ -3022,7 +3023,7 @@
         <v>0.51695733681758738</v>
       </c>
       <c r="I78" s="0">
-        <v>0.2621596393318899</v>
+        <v>0.26215963933188991</v>
       </c>
       <c r="J78" s="0">
         <v>0.42326094957673871</v>
@@ -3045,7 +3046,7 @@
         <v>0.25995764592500514</v>
       </c>
       <c r="D79" s="0">
-        <v>0.14906354434640431</v>
+        <v>0.14906354434640432</v>
       </c>
       <c r="E79" s="0">
         <v>0.32876875801784033</v>
@@ -3092,7 +3093,7 @@
         <v>0.38387366735800277</v>
       </c>
       <c r="G80" s="0">
-        <v>0.32186682760008017</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H80" s="0">
         <v>0.40334033971482097</v>
@@ -3133,7 +3134,7 @@
         <v>0.26151679742506517</v>
       </c>
       <c r="H81" s="0">
-        <v>0.42606373913537426</v>
+        <v>0.42606373913537427</v>
       </c>
       <c r="I81" s="0">
         <v>0.12909376179221851</v>
@@ -3168,7 +3169,7 @@
         <v>0.26561874613397646</v>
       </c>
       <c r="G82" s="0">
-        <v>0.341983504325089</v>
+        <v>0.34198350432508901</v>
       </c>
       <c r="H82" s="0">
         <v>0.26699994319150416</v>
@@ -3525,7 +3526,7 @@
         <v>1.2886597938144317</v>
       </c>
       <c r="L91" s="0">
-        <v>0.018660778154449022</v>
+        <v>0.018660778154449023</v>
       </c>
     </row>
     <row r="92">
@@ -3551,7 +3552,7 @@
         <v>0.060350030175015036</v>
       </c>
       <c r="H92" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.06817019826165989</v>
       </c>
       <c r="I92" s="0">
         <v>0.01588846298981151</v>
